--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F4FDC7-AF48-4BD1-B598-E7798041AF51}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A35B240-1A9D-4BC3-813B-CE484B2CCFFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="198">
   <si>
     <t>name</t>
   </si>
@@ -496,6 +496,129 @@
   </si>
   <si>
     <t>station.jpg</t>
+  </si>
+  <si>
+    <t>Estelle Manor</t>
+  </si>
+  <si>
+    <t>estelle-manor</t>
+  </si>
+  <si>
+    <t>An award-winning country house hotel and private members’ club set in a Grade-II listed landmark house on a 85-acre Oxfordshire estate. Surrounded by over 3,000 acres of beautiful parkland and gardens.</t>
+  </si>
+  <si>
+    <t>Luxury Cotswolds hotel</t>
+  </si>
+  <si>
+    <t>Eynsham Park, Oxfordshire</t>
+  </si>
+  <si>
+    <t>OX29 6PN</t>
+  </si>
+  <si>
+    <t>estell.jpg</t>
+  </si>
+  <si>
+    <t>Soho Farmhouse</t>
+  </si>
+  <si>
+    <t>RH England</t>
+  </si>
+  <si>
+    <t>The Marlstone Tavern</t>
+  </si>
+  <si>
+    <t>Quince &amp; Clover</t>
+  </si>
+  <si>
+    <t>Double Red Duke BV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double Red Duke  </t>
+  </si>
+  <si>
+    <t>Mollies Motel</t>
+  </si>
+  <si>
+    <t>Blakes Kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bull </t>
+  </si>
+  <si>
+    <t>The Bell</t>
+  </si>
+  <si>
+    <t>Muddy Duck</t>
+  </si>
+  <si>
+    <t>Imperial Garden</t>
+  </si>
+  <si>
+    <t>Landmark Hotel</t>
+  </si>
+  <si>
+    <t>Heythrop Park</t>
+  </si>
+  <si>
+    <t>hotel|restaurant</t>
+  </si>
+  <si>
+    <t>café</t>
+  </si>
+  <si>
+    <t>bakery|café</t>
+  </si>
+  <si>
+    <t>hethe</t>
+  </si>
+  <si>
+    <t>milton keynes</t>
+  </si>
+  <si>
+    <t>marylebone</t>
+  </si>
+  <si>
+    <t>soho-farmhouse</t>
+  </si>
+  <si>
+    <t>rh-england</t>
+  </si>
+  <si>
+    <t>quince-clover</t>
+  </si>
+  <si>
+    <t>mollies-motel</t>
+  </si>
+  <si>
+    <t>blakes-kitchen</t>
+  </si>
+  <si>
+    <t>the-bull</t>
+  </si>
+  <si>
+    <t>the-bell</t>
+  </si>
+  <si>
+    <t>muddy-duck</t>
+  </si>
+  <si>
+    <t>imperial-garden</t>
+  </si>
+  <si>
+    <t>landmark-hotel</t>
+  </si>
+  <si>
+    <t>heythrop-park</t>
+  </si>
+  <si>
+    <t>marlstone-tavern</t>
+  </si>
+  <si>
+    <t>red-duke</t>
+  </si>
+  <si>
+    <t>red-duke-bv</t>
   </si>
 </sst>
 </file>
@@ -813,10 +936,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -1682,6 +1805,330 @@
         <v>29</v>
       </c>
     </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" t="s">
+        <v>162</v>
+      </c>
+      <c r="P22" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>173</v>
+      </c>
+      <c r="B32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A35B240-1A9D-4BC3-813B-CE484B2CCFFB}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CAA9929-3EAA-4CFD-8DDB-752D13F51815}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="203">
   <si>
     <t>name</t>
   </si>
@@ -619,6 +619,21 @@
   </si>
   <si>
     <t>red-duke-bv</t>
+  </si>
+  <si>
+    <t>Thyme</t>
+  </si>
+  <si>
+    <t>thyme</t>
+  </si>
+  <si>
+    <t>Lechlade</t>
+  </si>
+  <si>
+    <t>The Lakes by Yoo</t>
+  </si>
+  <si>
+    <t>the-lakes-yoo</t>
   </si>
 </sst>
 </file>
@@ -936,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -2129,6 +2144,58 @@
         <v>29</v>
       </c>
     </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CAA9929-3EAA-4CFD-8DDB-752D13F51815}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74778B77-E94D-49DF-924F-8A266D4B001D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="222">
   <si>
     <t>name</t>
   </si>
@@ -531,9 +531,6 @@
     <t>Quince &amp; Clover</t>
   </si>
   <si>
-    <t>Double Red Duke BV</t>
-  </si>
-  <si>
     <t xml:space="preserve">Double Red Duke  </t>
   </si>
   <si>
@@ -634,6 +631,66 @@
   </si>
   <si>
     <t>the-lakes-yoo</t>
+  </si>
+  <si>
+    <t>Ottolenghi</t>
+  </si>
+  <si>
+    <t>OX26 6WN</t>
+  </si>
+  <si>
+    <t>Itsu</t>
+  </si>
+  <si>
+    <t>The Double Red Duke</t>
+  </si>
+  <si>
+    <t>Ralph's Coffee</t>
+  </si>
+  <si>
+    <t>ralphs</t>
+  </si>
+  <si>
+    <t>Crêperie Angélie</t>
+  </si>
+  <si>
+    <t>angelie</t>
+  </si>
+  <si>
+    <t>Humble Crumble</t>
+  </si>
+  <si>
+    <t>crumble</t>
+  </si>
+  <si>
+    <t>Oliphant's</t>
+  </si>
+  <si>
+    <t>oliphants</t>
+  </si>
+  <si>
+    <t>Ladurée</t>
+  </si>
+  <si>
+    <t>laduree</t>
+  </si>
+  <si>
+    <t>Pret A Manger</t>
+  </si>
+  <si>
+    <t>pret</t>
+  </si>
+  <si>
+    <t>Fortnum &amp; Mason</t>
+  </si>
+  <si>
+    <t>fortnum</t>
+  </si>
+  <si>
+    <t>Tease</t>
+  </si>
+  <si>
+    <t>tease</t>
   </si>
 </sst>
 </file>
@@ -951,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -1863,7 +1920,7 @@
         <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s">
         <v>97</v>
@@ -1883,7 +1940,7 @@
         <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -1903,7 +1960,7 @@
         <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -1923,10 +1980,10 @@
         <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
         <v>140</v>
@@ -1940,16 +1997,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
@@ -1960,16 +2020,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
@@ -1980,13 +2040,13 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
         <v>140</v>
@@ -2000,13 +2060,13 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" t="s">
         <v>140</v>
@@ -2020,10 +2080,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
       </c>
       <c r="D31" t="s">
         <v>44</v>
@@ -2040,10 +2103,13 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>189</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
       </c>
       <c r="D32" t="s">
         <v>44</v>
@@ -2060,16 +2126,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>190</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
       </c>
       <c r="D33" t="s">
         <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
@@ -2080,16 +2149,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
@@ -2100,10 +2169,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C35" t="s">
         <v>96</v>
@@ -2112,7 +2181,7 @@
         <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
@@ -2123,10 +2192,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
         <v>96</v>
@@ -2146,22 +2215,22 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" t="s">
         <v>198</v>
-      </c>
-      <c r="B37" t="s">
-        <v>199</v>
       </c>
       <c r="C37" t="s">
         <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E37" t="s">
         <v>140</v>
       </c>
       <c r="H37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
@@ -2172,10 +2241,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
         <v>201</v>
-      </c>
-      <c r="B38" t="s">
-        <v>202</v>
       </c>
       <c r="C38" t="s">
         <v>96</v>
@@ -2187,13 +2256,192 @@
         <v>140</v>
       </c>
       <c r="H38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>178</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>208</v>
+      </c>
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>212</v>
+      </c>
+      <c r="B44" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>218</v>
+      </c>
+      <c r="B47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74778B77-E94D-49DF-924F-8A266D4B001D}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1936D4C-13FC-42F1-888D-252B5C8E244C}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -561,12 +561,6 @@
     <t>hotel|restaurant</t>
   </si>
   <si>
-    <t>café</t>
-  </si>
-  <si>
-    <t>bakery|café</t>
-  </si>
-  <si>
     <t>hethe</t>
   </si>
   <si>
@@ -691,6 +685,12 @@
   </si>
   <si>
     <t>tease</t>
+  </si>
+  <si>
+    <t>cafe</t>
+  </si>
+  <si>
+    <t>bakery|cafe</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1920,7 @@
         <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
         <v>97</v>
@@ -1940,7 +1940,7 @@
         <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -1960,7 +1960,7 @@
         <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -1980,10 +1980,10 @@
         <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
         <v>140</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -2023,7 +2023,7 @@
         <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
         <v>177</v>
@@ -2043,7 +2043,7 @@
         <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D29" t="s">
         <v>177</v>
@@ -2063,10 +2063,10 @@
         <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="E30" t="s">
         <v>140</v>
@@ -2083,7 +2083,7 @@
         <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -2106,7 +2106,7 @@
         <v>172</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
@@ -2129,7 +2129,7 @@
         <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2138,7 +2138,7 @@
         <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
@@ -2152,13 +2152,13 @@
         <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
@@ -2172,7 +2172,7 @@
         <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
         <v>96</v>
@@ -2181,7 +2181,7 @@
         <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
@@ -2195,7 +2195,7 @@
         <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C36" t="s">
         <v>96</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s">
         <v>96</v>
@@ -2230,7 +2230,7 @@
         <v>140</v>
       </c>
       <c r="H37" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
         <v>96</v>
@@ -2256,7 +2256,7 @@
         <v>140</v>
       </c>
       <c r="H38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2285,15 +2285,15 @@
         <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -2310,16 +2310,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -2327,16 +2327,16 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
@@ -2344,16 +2344,16 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C43" t="s">
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
@@ -2361,16 +2361,16 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C44" t="s">
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
@@ -2378,16 +2378,16 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
@@ -2395,16 +2395,16 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C46" t="s">
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
@@ -2412,16 +2412,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
@@ -2429,16 +2429,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C48" t="s">
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1936D4C-13FC-42F1-888D-252B5C8E244C}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A0B4EA-DD2B-4C34-BEB9-1EC83F3BEA7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="222">
   <si>
     <t>name</t>
   </si>
@@ -2287,6 +2287,12 @@
       <c r="I39" t="s">
         <v>201</v>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -2307,6 +2313,12 @@
       <c r="H40" t="s">
         <v>25</v>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -2324,6 +2336,12 @@
       <c r="E41" t="s">
         <v>23</v>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -2341,6 +2359,12 @@
       <c r="E42" t="s">
         <v>23</v>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -2358,6 +2382,12 @@
       <c r="E43" t="s">
         <v>23</v>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -2375,6 +2405,12 @@
       <c r="E44" t="s">
         <v>23</v>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -2392,6 +2428,12 @@
       <c r="E45" t="s">
         <v>23</v>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -2409,6 +2451,12 @@
       <c r="E46" t="s">
         <v>23</v>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -2426,6 +2474,12 @@
       <c r="E47" t="s">
         <v>23</v>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -2442,6 +2496,12 @@
       </c>
       <c r="E48" t="s">
         <v>23</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A0B4EA-DD2B-4C34-BEB9-1EC83F3BEA7D}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32F946FA-782A-41AA-ADDD-C825A9831142}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="223">
   <si>
     <t>name</t>
   </si>
@@ -691,6 +691,9 @@
   </si>
   <si>
     <t>bakery|cafe</t>
+  </si>
+  <si>
+    <t>distance minutes</t>
   </si>
 </sst>
 </file>
@@ -1008,30 +1011,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="87.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="87.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1048,49 +1052,52 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1106,35 +1113,38 @@
       <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="b">
+      <c r="R2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
       <c r="S2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1150,35 +1160,38 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" t="b">
+      <c r="R3" t="b">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
-        <v>29</v>
-      </c>
       <c r="S3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1194,32 +1207,35 @@
       <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>40</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>27</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1235,35 +1251,38 @@
       <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>27</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" t="b">
+      <c r="R5" t="b">
         <v>1</v>
       </c>
-      <c r="R5" t="s">
-        <v>29</v>
-      </c>
       <c r="S5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1279,32 +1298,35 @@
       <c r="E6" t="s">
         <v>54</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>57</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>58</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>27</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>59</v>
       </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1320,29 +1342,32 @@
       <c r="E7" t="s">
         <v>62</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>63</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>64</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>65</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>27</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>66</v>
       </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -1358,29 +1383,32 @@
       <c r="E8" t="s">
         <v>62</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
         <v>70</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>71</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>72</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>27</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>73</v>
       </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
@@ -1396,29 +1424,32 @@
       <c r="E9" t="s">
         <v>62</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9" t="s">
         <v>76</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>77</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>72</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>27</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>78</v>
       </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -1434,29 +1465,32 @@
       <c r="E10" t="s">
         <v>82</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
         <v>83</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>84</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>85</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>27</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>86</v>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1472,29 +1506,32 @@
       <c r="E11" t="s">
         <v>89</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
         <v>90</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>91</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>27</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>93</v>
       </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1510,29 +1547,32 @@
       <c r="E12" t="s">
         <v>54</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12" t="s">
         <v>98</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>99</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>57</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>27</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>100</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="R12" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -1548,29 +1588,32 @@
       <c r="E13" t="s">
         <v>62</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
         <v>103</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>104</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>65</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>27</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>105</v>
       </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -1586,29 +1629,32 @@
       <c r="E14" t="s">
         <v>62</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
         <v>108</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>109</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>65</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>27</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>110</v>
       </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -1624,32 +1670,35 @@
       <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>114</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>115</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>65</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>27</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>116</v>
       </c>
-      <c r="Q15" t="b">
+      <c r="R15" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="s">
-        <v>29</v>
-      </c>
       <c r="S15" t="s">
+        <v>29</v>
+      </c>
+      <c r="T15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -1665,29 +1714,32 @@
       <c r="E16" t="s">
         <v>62</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
         <v>121</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>122</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>65</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>27</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>123</v>
       </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -1703,29 +1755,32 @@
       <c r="E17" t="s">
         <v>127</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
         <v>128</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>129</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>130</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>27</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>131</v>
       </c>
-      <c r="Q17" t="b">
+      <c r="R17" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>132</v>
       </c>
@@ -1741,29 +1796,32 @@
       <c r="E18" t="s">
         <v>134</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
         <v>135</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>136</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>137</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>27</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>138</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="R18" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>
@@ -1779,29 +1837,32 @@
       <c r="E19" t="s">
         <v>140</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
         <v>141</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>142</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>139</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>27</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>143</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="R19" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -1817,29 +1878,32 @@
       <c r="E20" t="s">
         <v>62</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20" t="s">
         <v>147</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>148</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>65</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>27</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>149</v>
       </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -1855,29 +1919,32 @@
       <c r="E21" t="s">
         <v>62</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>154</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>155</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>65</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>27</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>156</v>
       </c>
-      <c r="Q21" t="b">
+      <c r="R21" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>157</v>
       </c>
@@ -1893,29 +1960,32 @@
       <c r="E22" t="s">
         <v>140</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
         <v>160</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>159</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>161</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>162</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>163</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="R22" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>164</v>
       </c>
@@ -1928,14 +1998,17 @@
       <c r="E23" t="s">
         <v>140</v>
       </c>
-      <c r="Q23" t="b">
+      <c r="F23">
+        <v>35</v>
+      </c>
+      <c r="R23" t="b">
         <v>1</v>
       </c>
-      <c r="R23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>165</v>
       </c>
@@ -1948,14 +2021,17 @@
       <c r="E24" t="s">
         <v>82</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="F24">
+        <v>17</v>
+      </c>
+      <c r="R24" t="b">
         <v>1</v>
       </c>
-      <c r="R24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>166</v>
       </c>
@@ -1968,14 +2044,17 @@
       <c r="E25" t="s">
         <v>82</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="F25">
+        <v>26</v>
+      </c>
+      <c r="R25" t="b">
         <v>1</v>
       </c>
-      <c r="R25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>167</v>
       </c>
@@ -1988,14 +2067,17 @@
       <c r="E26" t="s">
         <v>140</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="F26">
+        <v>32</v>
+      </c>
+      <c r="R26" t="b">
         <v>1</v>
       </c>
-      <c r="R26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>203</v>
       </c>
@@ -2011,14 +2093,17 @@
       <c r="E27" t="s">
         <v>23</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>168</v>
       </c>
@@ -2031,14 +2116,17 @@
       <c r="E28" t="s">
         <v>62</v>
       </c>
-      <c r="Q28" t="b">
+      <c r="F28">
+        <v>41</v>
+      </c>
+      <c r="R28" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -2051,14 +2139,17 @@
       <c r="E29" t="s">
         <v>140</v>
       </c>
-      <c r="Q29" t="b">
+      <c r="F29">
+        <v>32</v>
+      </c>
+      <c r="R29" t="b">
         <v>1</v>
       </c>
-      <c r="R29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>170</v>
       </c>
@@ -2071,14 +2162,17 @@
       <c r="E30" t="s">
         <v>140</v>
       </c>
-      <c r="Q30" t="b">
+      <c r="F30">
+        <v>41</v>
+      </c>
+      <c r="R30" t="b">
         <v>1</v>
       </c>
-      <c r="R30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>171</v>
       </c>
@@ -2094,14 +2188,17 @@
       <c r="E31" t="s">
         <v>140</v>
       </c>
-      <c r="Q31" t="b">
+      <c r="F31">
+        <v>34</v>
+      </c>
+      <c r="R31" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>172</v>
       </c>
@@ -2117,14 +2214,17 @@
       <c r="E32" t="s">
         <v>140</v>
       </c>
-      <c r="Q32" t="b">
+      <c r="F32">
+        <v>34</v>
+      </c>
+      <c r="R32" t="b">
         <v>1</v>
       </c>
-      <c r="R32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>173</v>
       </c>
@@ -2140,14 +2240,17 @@
       <c r="E33" t="s">
         <v>178</v>
       </c>
-      <c r="Q33" t="b">
+      <c r="F33">
+        <v>16</v>
+      </c>
+      <c r="R33" t="b">
         <v>1</v>
       </c>
-      <c r="R33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -2160,14 +2263,17 @@
       <c r="E34" t="s">
         <v>179</v>
       </c>
-      <c r="Q34" t="b">
+      <c r="F34">
+        <v>41</v>
+      </c>
+      <c r="R34" t="b">
         <v>1</v>
       </c>
-      <c r="R34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>175</v>
       </c>
@@ -2183,14 +2289,17 @@
       <c r="E35" t="s">
         <v>180</v>
       </c>
-      <c r="Q35" t="b">
+      <c r="F35">
+        <v>90</v>
+      </c>
+      <c r="R35" t="b">
         <v>1</v>
       </c>
-      <c r="R35" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>176</v>
       </c>
@@ -2206,14 +2315,17 @@
       <c r="E36" t="s">
         <v>140</v>
       </c>
-      <c r="Q36" t="b">
+      <c r="F36">
+        <v>40</v>
+      </c>
+      <c r="R36" t="b">
         <v>1</v>
       </c>
-      <c r="R36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>195</v>
       </c>
@@ -2229,17 +2341,20 @@
       <c r="E37" t="s">
         <v>140</v>
       </c>
-      <c r="H37" t="s">
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="I37" t="s">
         <v>197</v>
       </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>198</v>
       </c>
@@ -2255,17 +2370,20 @@
       <c r="E38" t="s">
         <v>140</v>
       </c>
-      <c r="H38" t="s">
+      <c r="F38">
+        <v>50</v>
+      </c>
+      <c r="I38" t="s">
         <v>197</v>
       </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>200</v>
       </c>
@@ -2281,20 +2399,23 @@
       <c r="E39" t="s">
         <v>23</v>
       </c>
-      <c r="H39" t="s">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
         <v>25</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>201</v>
       </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -2310,17 +2431,20 @@
       <c r="E40" t="s">
         <v>23</v>
       </c>
-      <c r="H40" t="s">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
         <v>25</v>
       </c>
-      <c r="Q40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -2336,14 +2460,17 @@
       <c r="E41" t="s">
         <v>23</v>
       </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>206</v>
       </c>
@@ -2359,14 +2486,17 @@
       <c r="E42" t="s">
         <v>23</v>
       </c>
-      <c r="Q42" t="b">
-        <v>0</v>
-      </c>
-      <c r="R42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>208</v>
       </c>
@@ -2382,14 +2512,17 @@
       <c r="E43" t="s">
         <v>23</v>
       </c>
-      <c r="Q43" t="b">
-        <v>0</v>
-      </c>
-      <c r="R43" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>210</v>
       </c>
@@ -2405,14 +2538,17 @@
       <c r="E44" t="s">
         <v>23</v>
       </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>212</v>
       </c>
@@ -2428,14 +2564,17 @@
       <c r="E45" t="s">
         <v>23</v>
       </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>214</v>
       </c>
@@ -2451,14 +2590,17 @@
       <c r="E46" t="s">
         <v>23</v>
       </c>
-      <c r="Q46" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -2474,14 +2616,17 @@
       <c r="E47" t="s">
         <v>23</v>
       </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>218</v>
       </c>
@@ -2497,10 +2642,13 @@
       <c r="E48" t="s">
         <v>23</v>
       </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48" t="s">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48" t="s">
         <v>29</v>
       </c>
     </row>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32F946FA-782A-41AA-ADDD-C825A9831142}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76AEA12B-F72C-46BB-AB40-932E28B755D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="228">
   <si>
     <t>name</t>
   </si>
@@ -567,9 +567,6 @@
     <t>milton keynes</t>
   </si>
   <si>
-    <t>marylebone</t>
-  </si>
-  <si>
     <t>soho-farmhouse</t>
   </si>
   <si>
@@ -694,6 +691,24 @@
   </si>
   <si>
     <t>distance minutes</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Weston Manor Hotel</t>
+  </si>
+  <si>
+    <t>weston-manor</t>
+  </si>
+  <si>
+    <t>weston-on-the-green</t>
+  </si>
+  <si>
+    <t>Weston On The Green</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -1052,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1990,7 +2005,7 @@
         <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
         <v>97</v>
@@ -2013,7 +2028,7 @@
         <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -2036,7 +2051,7 @@
         <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -2059,10 +2074,10 @@
         <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E26" t="s">
         <v>140</v>
@@ -2079,10 +2094,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -2108,7 +2123,7 @@
         <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D28" t="s">
         <v>177</v>
@@ -2131,7 +2146,7 @@
         <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
         <v>177</v>
@@ -2154,10 +2169,10 @@
         <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E30" t="s">
         <v>140</v>
@@ -2177,7 +2192,7 @@
         <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -2203,7 +2218,7 @@
         <v>172</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
@@ -2229,7 +2244,7 @@
         <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2255,7 +2270,7 @@
         <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -2278,7 +2293,7 @@
         <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
         <v>96</v>
@@ -2287,10 +2302,13 @@
         <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="F35">
         <v>90</v>
+      </c>
+      <c r="I35" t="s">
+        <v>223</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
@@ -2304,7 +2322,7 @@
         <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s">
         <v>96</v>
@@ -2327,10 +2345,10 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" t="s">
         <v>195</v>
-      </c>
-      <c r="B37" t="s">
-        <v>196</v>
       </c>
       <c r="C37" t="s">
         <v>96</v>
@@ -2345,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -2356,10 +2374,10 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" t="s">
         <v>198</v>
-      </c>
-      <c r="B38" t="s">
-        <v>199</v>
       </c>
       <c r="C38" t="s">
         <v>96</v>
@@ -2374,7 +2392,7 @@
         <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
@@ -2385,10 +2403,10 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2406,7 +2424,7 @@
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -2417,10 +2435,10 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -2446,16 +2464,16 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" t="s">
         <v>204</v>
-      </c>
-      <c r="B41" t="s">
-        <v>205</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -2472,16 +2490,16 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" t="s">
         <v>206</v>
-      </c>
-      <c r="B42" t="s">
-        <v>207</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
@@ -2498,16 +2516,16 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
         <v>208</v>
-      </c>
-      <c r="B43" t="s">
-        <v>209</v>
       </c>
       <c r="C43" t="s">
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
@@ -2524,16 +2542,16 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" t="s">
         <v>210</v>
-      </c>
-      <c r="B44" t="s">
-        <v>211</v>
       </c>
       <c r="C44" t="s">
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
@@ -2550,16 +2568,16 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" t="s">
         <v>212</v>
-      </c>
-      <c r="B45" t="s">
-        <v>213</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
@@ -2576,16 +2594,16 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" t="s">
         <v>214</v>
-      </c>
-      <c r="B46" t="s">
-        <v>215</v>
       </c>
       <c r="C46" t="s">
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
@@ -2602,16 +2620,16 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" t="s">
         <v>216</v>
-      </c>
-      <c r="B47" t="s">
-        <v>217</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
@@ -2628,16 +2646,16 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>217</v>
+      </c>
+      <c r="B48" t="s">
         <v>218</v>
-      </c>
-      <c r="B48" t="s">
-        <v>219</v>
       </c>
       <c r="C48" t="s">
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>
@@ -2649,6 +2667,35 @@
         <v>0</v>
       </c>
       <c r="S48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" t="s">
+        <v>226</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>227</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+      <c r="S49" t="s">
         <v>29</v>
       </c>
     </row>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76AEA12B-F72C-46BB-AB40-932E28B755D7}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5743A652-B7DD-41CE-8286-E553264BB2E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2687,7 +2687,7 @@
         <v>226</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I49" t="s">
         <v>227</v>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5743A652-B7DD-41CE-8286-E553264BB2E9}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F91D32E-9EC2-4A0F-94BB-6E3A0B474F76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="228">
   <si>
     <t>name</t>
   </si>
@@ -2007,6 +2007,9 @@
       <c r="B23" t="s">
         <v>180</v>
       </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
       <c r="D23" t="s">
         <v>97</v>
       </c>
@@ -2030,6 +2033,9 @@
       <c r="B24" t="s">
         <v>181</v>
       </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
@@ -2053,6 +2059,9 @@
       <c r="B25" t="s">
         <v>191</v>
       </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
       <c r="D25" t="s">
         <v>22</v>
       </c>
@@ -2076,6 +2085,9 @@
       <c r="B26" t="s">
         <v>182</v>
       </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
       <c r="D26" t="s">
         <v>219</v>
       </c>
@@ -2125,6 +2137,9 @@
       <c r="B28" t="s">
         <v>192</v>
       </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
       <c r="D28" t="s">
         <v>177</v>
       </c>
@@ -2148,6 +2163,9 @@
       <c r="B29" t="s">
         <v>183</v>
       </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
       <c r="D29" t="s">
         <v>177</v>
       </c>
@@ -2170,6 +2188,9 @@
       </c>
       <c r="B30" t="s">
         <v>184</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
       </c>
       <c r="D30" t="s">
         <v>220</v>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F91D32E-9EC2-4A0F-94BB-6E3A0B474F76}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F9F32B9-1094-4632-B234-071F6A4B10AA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="232">
   <si>
     <t>name</t>
   </si>
@@ -709,6 +709,18 @@
   </si>
   <si>
     <t>Weston On The Green</t>
+  </si>
+  <si>
+    <t>Esquires</t>
+  </si>
+  <si>
+    <t>esquires</t>
+  </si>
+  <si>
+    <t>graven-hill</t>
+  </si>
+  <si>
+    <t>Graven Hill</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -2720,6 +2732,35 @@
         <v>29</v>
       </c>
     </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>228</v>
+      </c>
+      <c r="B50" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="I50" t="s">
+        <v>231</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F9F32B9-1094-4632-B234-071F6A4B10AA}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CAC8C4-96F1-4170-9496-239E856DFE4F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="233">
   <si>
     <t>name</t>
   </si>
@@ -721,6 +721,9 @@
   </si>
   <si>
     <t>Graven Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Located by Marylebone station </t>
   </si>
 </sst>
 </file>
@@ -2340,6 +2343,9 @@
       <c r="F35">
         <v>90</v>
       </c>
+      <c r="G35" t="s">
+        <v>232</v>
+      </c>
       <c r="I35" t="s">
         <v>223</v>
       </c>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CAC8C4-96F1-4170-9496-239E856DFE4F}"/>
+  <xr:revisionPtr revIDLastSave="309" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13842A3F-FE0F-480E-9931-7F3FFDB96674}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="255">
   <si>
     <t>name</t>
   </si>
@@ -724,6 +724,72 @@
   </si>
   <si>
     <t xml:space="preserve">Located by Marylebone station </t>
+  </si>
+  <si>
+    <t>Farmer's Dog</t>
+  </si>
+  <si>
+    <t>Diddly Squat Farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawkstone Brewery </t>
+  </si>
+  <si>
+    <t>Sandy Lane Farm</t>
+  </si>
+  <si>
+    <t>Dunkertons</t>
+  </si>
+  <si>
+    <t>brewery</t>
+  </si>
+  <si>
+    <t>hawkstone</t>
+  </si>
+  <si>
+    <t>GL54 2HN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourton on the Water, Gloucestershire </t>
+  </si>
+  <si>
+    <t>GL52 6UT</t>
+  </si>
+  <si>
+    <t>Cheltenham, Gloucetershire</t>
+  </si>
+  <si>
+    <t>dunkertons</t>
+  </si>
+  <si>
+    <t>brewery|restaurant</t>
+  </si>
+  <si>
+    <t>Dayleford Farm</t>
+  </si>
+  <si>
+    <t>daylesford</t>
+  </si>
+  <si>
+    <t>farm-shop|restaurant</t>
+  </si>
+  <si>
+    <t>Worton Kitchen Garden</t>
+  </si>
+  <si>
+    <t>worton</t>
+  </si>
+  <si>
+    <t>sandy-lane</t>
+  </si>
+  <si>
+    <t>farmers-dog</t>
+  </si>
+  <si>
+    <t>diddly-squat</t>
+  </si>
+  <si>
+    <t>chilterns</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -2767,6 +2833,182 @@
         <v>29</v>
       </c>
     </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>246</v>
+      </c>
+      <c r="B51" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51">
+        <v>55</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+      <c r="S51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>234</v>
+      </c>
+      <c r="B52" t="s">
+        <v>253</v>
+      </c>
+      <c r="D52" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" t="s">
+        <v>140</v>
+      </c>
+      <c r="F52">
+        <v>45</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" t="s">
+        <v>252</v>
+      </c>
+      <c r="D53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53">
+        <v>40</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
+        <v>238</v>
+      </c>
+      <c r="E54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54">
+        <v>60</v>
+      </c>
+      <c r="I54" t="s">
+        <v>241</v>
+      </c>
+      <c r="J54" t="s">
+        <v>240</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" t="s">
+        <v>254</v>
+      </c>
+      <c r="F55">
+        <v>30</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56">
+        <v>60</v>
+      </c>
+      <c r="I56" t="s">
+        <v>243</v>
+      </c>
+      <c r="J56" t="s">
+        <v>242</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
+      <c r="S56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" t="s">
+        <v>250</v>
+      </c>
+      <c r="D57" t="s">
+        <v>248</v>
+      </c>
+      <c r="F57">
+        <v>25</v>
+      </c>
+      <c r="R57" t="b">
+        <v>0</v>
+      </c>
+      <c r="S57" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="309" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13842A3F-FE0F-480E-9931-7F3FFDB96674}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A8E41D8-022B-4B20-AB32-36AC1E1182AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="256">
   <si>
     <t>name</t>
   </si>
@@ -790,6 +790,9 @@
   </si>
   <si>
     <t>chilterns</t>
+  </si>
+  <si>
+    <t>eat-drink | things-to-do</t>
   </si>
 </sst>
 </file>
@@ -1112,6 +1115,7 @@
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2840,6 +2844,9 @@
       <c r="B51" t="s">
         <v>247</v>
       </c>
+      <c r="C51" t="s">
+        <v>255</v>
+      </c>
       <c r="D51" t="s">
         <v>248</v>
       </c>
@@ -2863,6 +2870,9 @@
       <c r="B52" t="s">
         <v>253</v>
       </c>
+      <c r="C52" t="s">
+        <v>112</v>
+      </c>
       <c r="D52" t="s">
         <v>81</v>
       </c>
@@ -2886,6 +2896,9 @@
       <c r="B53" t="s">
         <v>252</v>
       </c>
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
       <c r="D53" t="s">
         <v>44</v>
       </c>
@@ -2941,6 +2954,9 @@
       <c r="B55" t="s">
         <v>251</v>
       </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
       <c r="D55" t="s">
         <v>81</v>
       </c>
@@ -2965,7 +2981,7 @@
         <v>244</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
         <v>245</v>
@@ -2995,6 +3011,9 @@
       </c>
       <c r="B57" t="s">
         <v>250</v>
+      </c>
+      <c r="C57" t="s">
+        <v>255</v>
       </c>
       <c r="D57" t="s">
         <v>248</v>

--- a/data/places_master.xlsx
+++ b/data/places_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lovewue-my.sharepoint.com/personal/richard_lovewue_com/Documents/Documents 1/GitHub/bicesterguide/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A8E41D8-022B-4B20-AB32-36AC1E1182AB}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_AD4DB114E441178AC67DF48AFED5DF0A693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80222ED3-BDEB-4F97-AB1C-9F7BE34B3AAC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="261">
   <si>
     <t>name</t>
   </si>
@@ -793,6 +793,21 @@
   </si>
   <si>
     <t>eat-drink | things-to-do</t>
+  </si>
+  <si>
+    <t>rectory-farm</t>
+  </si>
+  <si>
+    <t>farm-shop|café</t>
+  </si>
+  <si>
+    <t>Rectory Farm PYO</t>
+  </si>
+  <si>
+    <t>oxfordshire</t>
+  </si>
+  <si>
+    <t>Pick your own farm with café and shop.</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -3018,6 +3033,9 @@
       <c r="D57" t="s">
         <v>248</v>
       </c>
+      <c r="E57" t="s">
+        <v>140</v>
+      </c>
       <c r="F57">
         <v>25</v>
       </c>
@@ -3025,6 +3043,35 @@
         <v>0</v>
       </c>
       <c r="S57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" t="s">
+        <v>256</v>
+      </c>
+      <c r="C58" t="s">
+        <v>255</v>
+      </c>
+      <c r="D58" t="s">
+        <v>257</v>
+      </c>
+      <c r="E58" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>260</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+      <c r="S58" t="s">
         <v>29</v>
       </c>
     </row>
